--- a/ABA_mining/outputs/eval/task3/check-in/llama3.2/zero_shot/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/check-in/llama3.2/zero_shot/EVAL_SUMMARY.xlsx
@@ -544,13 +544,13 @@
         <v>0.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6170212765957447</v>
+        <v>0.617021</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4853556485355649</v>
+        <v>0.485356</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5119047619047619</v>
+        <v>0.5119050000000001</v>
       </c>
     </row>
     <row r="3">
@@ -600,16 +600,16 @@
         <v>37</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3931034482758621</v>
+        <v>0.393103</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6063829787234043</v>
+        <v>0.606383</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4769874476987448</v>
+        <v>0.476987</v>
       </c>
       <c r="O3" t="n">
-        <v>0.503968253968254</v>
+        <v>0.503968</v>
       </c>
     </row>
     <row r="4">
@@ -659,16 +659,16 @@
         <v>36</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3972602739726027</v>
+        <v>0.39726</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6170212765957447</v>
+        <v>0.617021</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.483333</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5079365079365079</v>
+        <v>0.507937</v>
       </c>
     </row>
   </sheetData>
@@ -784,16 +784,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.3967889908256881</v>
+        <v>0.396789</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6134751773049646</v>
+        <v>0.613475</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4818941504178272</v>
+        <v>0.481894</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5079365079365079</v>
+        <v>0.507937</v>
       </c>
       <c r="J2" t="n">
         <v>756</v>
